--- a/tests/langchain/fixtures/files/invoice.xlsx
+++ b/tests/langchain/fixtures/files/invoice.xlsx
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1234.56</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="5">
